--- a/coretp/plans/hypervisor_interrupts/Hypervisor_Interrupts_TP.xlsx
+++ b/coretp/plans/hypervisor_interrupts/Hypervisor_Interrupts_TP.xlsx
@@ -3,10 +3,10 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="33600" yWindow="500" windowWidth="33600" windowHeight="37280" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="33600" yWindow="500" windowWidth="33600" windowHeight="37280" tabRatio="600" autoFilterDateGrouping="true"/>
   </bookViews>
   <sheets>
-    <sheet name="Hypervisor_Interrupts" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Hypervisor_Interrupts" sheetId="1" r:id="rId1" state="visible"/>
   </sheets>
   <definedNames>
     <definedName name="Actual">(PeriodInActual*(#REF!&gt;0))*PeriodInPlan</definedName>
@@ -19,12 +19,128 @@
     <definedName name="Plan">PeriodInPlan*(#REF!&gt;0)</definedName>
     <definedName name="TitleRegion..BO60">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191028" fullCalcOnLoad="1"/>
+  <calcPr calcId="191028" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+  <si>
+    <t># SID_HINTR_002
+CsrWrite(csr_name="menvcfg", set_mask=(1 &lt;&lt; 63))
+CsrWrite(csr_name="mcounteren", set_mask=0x2)
+CsrWrite(csr_name="hcounteren", set_mask=0x2)
+CsrWrite(csr_name="henvcfg", set_mask=(1 &lt;&lt; 63))
+Comment(comment="VS-interrupts from M-mode, delegated past M to HS, hideleg=0 -&gt; pending")
+DelegateInterrupt(causes=(), handler_mode=ExceptionHandlerMode.VS)
+EnableInterrupts(causes=(VSEI,), handler_mode=ExceptionHandlerMode.HS, global_enable=False)
+TriggerInterrupt(cause=VSEI)
+TriggerInterrupt(cause=VSSI)
+TriggerInterrupt(cause=VSTI)
+read_hip = CsrRead(csr_name="hip")
+AssertEqual(src1=read_hip, src2=VS_MASK)
+ClearInterrupt(cause=VSEI)
+ClearInterrupt(cause=VSSI)
+ClearInterrupt(cause=VSTI)</t>
+  </si>
+  <si>
+    <t># SID_HINTR_003
+CsrWrite(csr_name="menvcfg", set_mask=(1 &lt;&lt; 63))
+CsrWrite(csr_name="mcounteren", set_mask=0x2)
+CsrWrite(csr_name="hcounteren", set_mask=0x2)
+CsrWrite(csr_name="henvcfg", set_mask=(1 &lt;&lt; 63))
+Comment(comment="VS-interrupts/SGEI serviced in HS: sstatus.sie=1 &amp; hie[*]=1 &amp; hideleg=0")
+DelegateInterrupt(causes=(), handler_mode=ExceptionHandlerMode.VS)
+DelegateInterrupt(causes=(SGEI,), handler_mode=ExceptionHandlerMode.HS)
+ConfigureInterruptMode(mode=InterruptMode.DIRECT, handler_mode=ExceptionHandlerMode.HS)
+CsrWrite(csr_name="hie", set_mask=VS_MASK | SGEIP)
+EnableInterrupts(causes=(SSI, STI, SEI, VSEI, SGEI), handler_mode=ExceptionHandlerMode.HS, global_enable=True)
+AssertInterrupt(cause=VSEI, code=[TriggerInterrupt(cause=VSEI)], expected_handler_mode=ExceptionHandlerMode.HS)
+AssertInterrupt(cause=VSSI, code=[TriggerInterrupt(cause=VSSI)], expected_handler_mode=ExceptionHandlerMode.HS)
+AssertInterrupt(cause=VSTI, code=[TriggerInterrupt(cause=VSTI)], expected_handler_mode=ExceptionHandlerMode.HS)
+AssertInterrupt(cause=SGEI, code=[TriggerInterrupt(cause=SGEI)], expected_handler_mode=ExceptionHandlerMode.HS)
+ClearInterrupt(cause=VSEI)
+ClearInterrupt(cause=VSSI)
+ClearInterrupt(cause=VSTI)
+ClearInterrupt(cause=SGEI)
+DisableInterrupts(causes=(SSI, STI, SEI), handler_mode=ExceptionHandlerMode.HS)</t>
+  </si>
+  <si>
+    <t># SID_HINTR_004
+CsrWrite(csr_name="menvcfg", set_mask=(1 &lt;&lt; 63))
+CsrWrite(csr_name="mcounteren", set_mask=0x2)
+CsrWrite(csr_name="hcounteren", set_mask=0x2)
+CsrWrite(csr_name="henvcfg", set_mask=(1 &lt;&lt; 63))
+Comment(comment="VS-interrupts pending in HS: sstatus.sie=1 but hie[*]=0, hideleg=0")
+DelegateInterrupt(causes=(), handler_mode=ExceptionHandlerMode.VS)
+DelegateInterrupt(causes=(SGEI,), handler_mode=ExceptionHandlerMode.HS)
+ConfigureInterruptMode(mode=InterruptMode.DIRECT, handler_mode=ExceptionHandlerMode.HS)
+EnableInterrupts(causes=(VSEI, SGEI), handler_mode=ExceptionHandlerMode.HS, global_enable=True)
+CsrWrite(csr_name="hie", clear_mask=VS_MASK | SGEIP)
+TriggerInterrupt(cause=VSEI)
+TriggerInterrupt(cause=VSSI)
+TriggerInterrupt(cause=VSTI)
+TriggerInterrupt(cause=SGEI)
+read_hip = CsrRead(csr_name="hip")
+AssertEqual(src1=read_hip, src2=VS_MASK | SGEIP)
+ClearInterrupt(cause=VSEI)
+ClearInterrupt(cause=VSSI)
+ClearInterrupt(cause=VSTI)
+ClearInterrupt(cause=SGEI)
+DisableInterrupts(causes=(), handler_mode=ExceptionHandlerMode.HS)</t>
+  </si>
+  <si>
+    <t># SID_HINTR_005
+CsrWrite(csr_name="menvcfg", set_mask=(1 &lt;&lt; 63))
+CsrWrite(csr_name="mcounteren", set_mask=0x2)
+CsrWrite(csr_name="hcounteren", set_mask=0x2)
+CsrWrite(csr_name="henvcfg", set_mask=(1 &lt;&lt; 63))
+Comment(comment="VS-interrupts pending in HS: sstatus.sie=0, hideleg=0")
+DelegateInterrupt(causes=(), handler_mode=ExceptionHandlerMode.VS)
+DelegateInterrupt(causes=(SGEI,), handler_mode=ExceptionHandlerMode.HS)
+ConfigureInterruptMode(mode=InterruptMode.DIRECT, handler_mode=ExceptionHandlerMode.HS)
+CsrWrite(csr_name="hie", set_mask=VS_MASK | SGEIP)
+EnableInterrupts(causes=(VSEI, SGEI), handler_mode=ExceptionHandlerMode.HS, global_enable=False)
+DisableInterrupts(causes=(), handler_mode=ExceptionHandlerMode.HS, global_disable=True)
+TriggerInterrupt(cause=VSEI)
+TriggerInterrupt(cause=VSSI)
+TriggerInterrupt(cause=VSTI)
+TriggerInterrupt(cause=SGEI)
+read_hip = CsrRead(csr_name="hip")
+AssertEqual(src1=read_hip, src2=VS_MASK | SGEIP)
+ClearInterrupt(cause=VSEI)
+ClearInterrupt(cause=VSSI)
+ClearInterrupt(cause=VSTI)
+ClearInterrupt(cause=SGEI)
+DisableInterrupts(causes=(), handler_mode=ExceptionHandlerMode.HS)</t>
+  </si>
+  <si>
+    <t># SID_HINTR_006
+CsrWrite(csr_name="menvcfg", set_mask=(1 &lt;&lt; 63))
+CsrWrite(csr_name="mcounteren", set_mask=0x2)
+CsrWrite(csr_name="hcounteren", set_mask=0x2)
+CsrWrite(csr_name="henvcfg", set_mask=(1 &lt;&lt; 63))
+Comment(comment="VS-interrupts from VS/VU/HU serviced in HS: hie[*]=1, hideleg=0, sstatus.sie=X")
+DelegateInterrupt(causes=(), handler_mode=ExceptionHandlerMode.VS)
+DelegateInterrupt(causes=(SGEI,), handler_mode=ExceptionHandlerMode.HS)
+ConfigureInterruptMode(mode=InterruptMode.DIRECT, handler_mode=ExceptionHandlerMode.HS)
+CsrWrite(csr_name="hie", set_mask=VS_MASK | SGEIP)
+EnableInterrupts(causes=(SSI, STI, SEI, VSEI, SGEI), handler_mode=ExceptionHandlerMode.HS, global_enable=False)
+AssertInterrupt(cause=VSEI, code=[TriggerInterrupt(cause=VSEI)], expected_handler_mode=ExceptionHandlerMode.HS)
+AssertInterrupt(cause=VSSI, code=[TriggerInterrupt(cause=VSSI)], expected_handler_mode=ExceptionHandlerMode.HS)
+AssertInterrupt(cause=VSTI, code=[TriggerInterrupt(cause=VSTI)], expected_handler_mode=ExceptionHandlerMode.HS)
+AssertInterrupt(cause=SGEI, code=[TriggerInterrupt(cause=SGEI)], expected_handler_mode=ExceptionHandlerMode.HS)
+ClearInterrupt(cause=VSEI)
+ClearInterrupt(cause=VSSI)
+ClearInterrupt(cause=VSTI)
+ClearInterrupt(cause=SGEI)
+DisableInterrupts(causes=(SSI, STI, SEI), handler_mode=ExceptionHandlerMode.HS)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <numFmts count="0"/>
   <fonts count="39">
     <font>
@@ -323,7 +439,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor auto="1"/>
+        <bgColor auto="true"/>
       </patternFill>
     </fill>
     <fill>
@@ -459,7 +575,7 @@
         <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </bottom>
       <diagonal/>
     </border>
@@ -470,20 +586,20 @@
         <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </bottom>
       <diagonal/>
     </border>
@@ -590,7 +706,7 @@
     <border>
       <left/>
       <right style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </right>
       <top/>
       <bottom/>
@@ -607,224 +723,230 @@
     </border>
   </borders>
   <cellStyleXfs count="23">
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="true">
+      <alignment horizontal="left" wrapText="true"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="2" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="true">
+      <alignment horizontal="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="true">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="6" borderId="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="9" fillId="6" borderId="1" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="8" borderId="0"/>
     <xf numFmtId="0" fontId="34" fillId="9" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="6"/>
   </cellStyleXfs>
-  <cellXfs count="53">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="55">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="false" pivotButton="false" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="false" pivotButton="false" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" quotePrefix="false" pivotButton="false" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="22">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="22" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="20" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="false" pivotButton="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="false" pivotButton="false" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="9" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="21">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="9" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="21">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="11" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="20" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="9" borderId="18" xfId="21" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="9" borderId="10" xfId="21" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="11" borderId="11" xfId="0" quotePrefix="false" pivotButton="false" applyAlignment="true">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="11" xfId="0" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="14" xfId="0" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="12" xfId="0" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="16" xfId="0" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="false" pivotButton="false" applyAlignment="true">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="21">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="21">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="22">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" xfId="0" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="14" xfId="0" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="16" xfId="0" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="13" xfId="0" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" xfId="21" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="9" xfId="21" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="11" xfId="20" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="11" xfId="0" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="11" xfId="0" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="12" xfId="20" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="13" xfId="0" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="0" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" xfId="0" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="17" xfId="20" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="15" xfId="0" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="14" xfId="0" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="17" xfId="20" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" xfId="0" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="7" xfId="22" quotePrefix="false" pivotButton="false" applyAlignment="true">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="22">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="8" xfId="22" quotePrefix="false" pivotButton="false" applyAlignment="true">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="22">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="22">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="10" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="22">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="22">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="22" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="10" borderId="7" xfId="22" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="10" borderId="8" xfId="22" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="22" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" quotePrefix="false" pivotButton="false"/>
+    <xf numFmtId="0" fontId="35" fillId="11" borderId="17" xfId="0" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" quotePrefix="false" pivotButton="false" applyAlignment="true">
+      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    </xf>
   </cellXfs>
   <cellStyles count="23">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -851,13 +973,13 @@
     <cellStyle name="Neutral" xfId="21" builtinId="28"/>
     <cellStyle name="Note" xfId="22" builtinId="10"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <colors/>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="152">
       <a:dk1>
@@ -1082,23 +1204,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="13" bestFit="1" customWidth="1" style="5" min="1" max="1"/>
-    <col width="28.83203125" bestFit="1" customWidth="1" style="5" min="2" max="2"/>
-    <col width="34.33203125" customWidth="1" style="5" min="3" max="3"/>
-    <col width="92.33203125" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
-    <col width="94.33203125" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
-    <col width="8.83203125" customWidth="1" style="6" min="6" max="8"/>
+    <col bestFit="true" customWidth="true" max="1" min="1" style="5" width="13"/>
+    <col bestFit="true" customWidth="true" max="2" min="2" style="5" width="28.83203125"/>
+    <col customWidth="true" max="3" min="3" style="5" width="34.33203125"/>
+    <col bestFit="true" customWidth="true" max="4" min="4" style="5" width="92.33203125"/>
+    <col bestFit="true" customWidth="true" max="5" min="5" style="5" width="94.33203125"/>
+    <col customWidth="true" max="8" min="6" style="6" width="8.83203125"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16" customHeight="1" s="5">
+    <row r="1" s="5" ht="16" customHeight="true">
       <c r="A1" s="46" t="inlineStr">
         <is>
           <t>Scenario details</t>
@@ -1111,7 +1233,7 @@
       <c r="F1" s="48" t="n"/>
       <c r="G1" s="48" t="n"/>
     </row>
-    <row r="2" ht="16" customHeight="1" s="5">
+    <row r="2" s="5" ht="16" customHeight="true">
       <c r="A2" s="21" t="inlineStr">
         <is>
           <t>Scenario ID</t>
@@ -1141,7 +1263,7 @@
       <c r="G2" s="4" t="n"/>
       <c r="H2" s="4" t="n"/>
     </row>
-    <row r="3" ht="365" customHeight="1" s="5">
+    <row r="3" s="5" ht="365" customHeight="true">
       <c r="A3" s="23" t="inlineStr">
         <is>
           <t>SID_HINTR_001</t>
@@ -1199,7 +1321,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="272" customHeight="1" s="5">
+    <row r="4" s="5" ht="272" customHeight="true">
       <c r="A4" s="23" t="inlineStr">
         <is>
           <t>SID_HINTR_002</t>
@@ -1226,29 +1348,11 @@
 </t>
         </is>
       </c>
-      <c r="E4" s="27" t="inlineStr">
-        <is>
-          <t># SID_HINTR_002
-CsrWrite(csr_name="menvcfg", set_mask=(1 &lt;&lt; 63))
-CsrWrite(csr_name="mcounteren", set_mask=0x2)
-CsrWrite(csr_name="hcounteren", set_mask=0x2)
-CsrWrite(csr_name="henvcfg", set_mask=(1 &lt;&lt; 63))
-Comment(comment="VS-interrupts from M-mode, delegated past M to HS, hideleg=0 -&gt; pending")
-CsrWrite(csr_name="mideleg", set_mask=VS_MASK | SGEIP)
-DelegateInterrupt(causes=(), handler_mode=ExceptionHandlerMode.VS)
-EnableInterrupts(causes=(VSEI,), handler_mode=ExceptionHandlerMode.HS, global_enable=False)
-TriggerInterrupt(cause=VSEI)
-TriggerInterrupt(cause=VSSI)
-TriggerInterrupt(cause=VSTI)
-read_hip = CsrRead(csr_name="hip")
-AssertEqual(src1=read_hip, src2=VS_MASK)
-ClearInterrupt(cause=VSEI)
-ClearInterrupt(cause=VSSI)
-ClearInterrupt(cause=VSTI)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="365" customHeight="1" s="5">
+      <c r="E4" s="27" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" s="5" ht="365" customHeight="true">
       <c r="A5" s="23" t="inlineStr">
         <is>
           <t>SID_HINTR_003</t>
@@ -1282,31 +1386,11 @@
 Note2: SGEI cannot be delegated to VS-mode (hideleg.12 = 0 always)</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
-        <is>
-          <t># SID_HINTR_003
-CsrWrite(csr_name="menvcfg", set_mask=(1 &lt;&lt; 63))
-CsrWrite(csr_name="mcounteren", set_mask=0x2)
-CsrWrite(csr_name="hcounteren", set_mask=0x2)
-CsrWrite(csr_name="henvcfg", set_mask=(1 &lt;&lt; 63))
-Comment(comment="VS-interrupts/SGEI serviced in HS: sstatus.sie=1 &amp; hie[*]=1 &amp; hideleg=0")
-DelegateInterrupt(causes=(), handler_mode=ExceptionHandlerMode.VS)
-ConfigureInterruptMode(mode=InterruptMode.DIRECT, handler_mode=ExceptionHandlerMode.HS)
-CsrWrite(csr_name="hie", set_mask=VS_MASK | SGEIP)
-EnableInterrupts(causes=(SSI, STI, SEI, VSEI), handler_mode=ExceptionHandlerMode.HS, global_enable=True)
-AssertInterrupt(cause=VSEI, code=[TriggerInterrupt(cause=VSEI)], expected_handler_mode=ExceptionHandlerMode.HS)
-AssertInterrupt(cause=VSSI, code=[TriggerInterrupt(cause=VSSI)], expected_handler_mode=ExceptionHandlerMode.HS)
-AssertInterrupt(cause=VSTI, code=[TriggerInterrupt(cause=VSTI)], expected_handler_mode=ExceptionHandlerMode.HS)
-AssertInterrupt(cause=SGEI, code=[TriggerInterrupt(cause=SGEI)], expected_handler_mode=ExceptionHandlerMode.HS)
-ClearInterrupt(cause=VSEI)
-ClearInterrupt(cause=VSSI)
-ClearInterrupt(cause=VSTI)
-ClearInterrupt(cause=SGEI)
-DisableInterrupts(causes=(SSI, STI, SEI), handler_mode=ExceptionHandlerMode.HS)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="335" customHeight="1" s="5">
+      <c r="E5" s="27" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" s="5" ht="335" customHeight="true">
       <c r="A6" s="23" t="inlineStr">
         <is>
           <t>SID_HINTR_004</t>
@@ -1332,33 +1416,11 @@
 </t>
         </is>
       </c>
-      <c r="E6" s="27" t="inlineStr">
-        <is>
-          <t># SID_HINTR_004
-CsrWrite(csr_name="menvcfg", set_mask=(1 &lt;&lt; 63))
-CsrWrite(csr_name="mcounteren", set_mask=0x2)
-CsrWrite(csr_name="hcounteren", set_mask=0x2)
-CsrWrite(csr_name="henvcfg", set_mask=(1 &lt;&lt; 63))
-Comment(comment="VS-interrupts pending in HS: sstatus.sie=1 but hie[*]=0, hideleg=0")
-DelegateInterrupt(causes=(), handler_mode=ExceptionHandlerMode.VS)
-ConfigureInterruptMode(mode=InterruptMode.DIRECT, handler_mode=ExceptionHandlerMode.HS)
-CsrWrite(csr_name="hie", clear_mask=VS_MASK | SGEIP)
-EnableInterrupts(causes=(VSEI, SGEI), handler_mode=ExceptionHandlerMode.HS, global_enable=True)
-TriggerInterrupt(cause=VSEI)
-TriggerInterrupt(cause=VSSI)
-TriggerInterrupt(cause=VSTI)
-TriggerInterrupt(cause=SGEI)
-read_hip = CsrRead(csr_name="hip")
-AssertEqual(src1=read_hip, src2=VS_MASK | SGEIP)
-ClearInterrupt(cause=VSEI)
-ClearInterrupt(cause=VSSI)
-ClearInterrupt(cause=VSTI)
-ClearInterrupt(cause=SGEI)
-DisableInterrupts(causes=(), handler_mode=ExceptionHandlerMode.HS)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="350" customHeight="1" s="5">
+      <c r="E6" s="27" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" s="5" ht="350" customHeight="true">
       <c r="A7" s="23" t="inlineStr">
         <is>
           <t>SID_HINTR_005</t>
@@ -1384,34 +1446,11 @@
 </t>
         </is>
       </c>
-      <c r="E7" s="27" t="inlineStr">
-        <is>
-          <t># SID_HINTR_005
-CsrWrite(csr_name="menvcfg", set_mask=(1 &lt;&lt; 63))
-CsrWrite(csr_name="mcounteren", set_mask=0x2)
-CsrWrite(csr_name="hcounteren", set_mask=0x2)
-CsrWrite(csr_name="henvcfg", set_mask=(1 &lt;&lt; 63))
-Comment(comment="VS-interrupts pending in HS: sstatus.sie=0, hideleg=0")
-DelegateInterrupt(causes=(), handler_mode=ExceptionHandlerMode.VS)
-ConfigureInterruptMode(mode=InterruptMode.DIRECT, handler_mode=ExceptionHandlerMode.HS)
-CsrWrite(csr_name="hie", set_mask=VS_MASK | SGEIP)
-EnableInterrupts(causes=(VSEI, SGEI), handler_mode=ExceptionHandlerMode.HS, global_enable=False)
-DisableInterrupts(causes=(), handler_mode=ExceptionHandlerMode.HS, global_disable=True)
-TriggerInterrupt(cause=VSEI)
-TriggerInterrupt(cause=VSSI)
-TriggerInterrupt(cause=VSTI)
-TriggerInterrupt(cause=SGEI)
-read_hip = CsrRead(csr_name="hip")
-AssertEqual(src1=read_hip, src2=VS_MASK | SGEIP)
-ClearInterrupt(cause=VSEI)
-ClearInterrupt(cause=VSSI)
-ClearInterrupt(cause=VSTI)
-ClearInterrupt(cause=SGEI)
-DisableInterrupts(causes=(), handler_mode=ExceptionHandlerMode.HS)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="365" customHeight="1" s="5">
+      <c r="E7" s="27" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" s="5" ht="365" customHeight="true">
       <c r="A8" s="23" t="inlineStr">
         <is>
           <t>SID_HINTR_006</t>
@@ -1444,31 +1483,11 @@
 (iv) SGEIP = hip.sgeip is read only =  bitwise-logical &amp; [ hgeip.i &amp;&amp; hgeie.i ] . If GEILEN is nonzero, GEILEN:1 is writable in hgeie, GEILEN_max = 63. Hstatus.VGEIN selects interrupt(i) in hgeip.i. hgeie selects the subset of GEI that cause a SGEI(HS-level) doesn't affect VSEIP generated using hgeip.i</t>
         </is>
       </c>
-      <c r="E8" s="27" t="inlineStr">
-        <is>
-          <t># SID_HINTR_006
-CsrWrite(csr_name="menvcfg", set_mask=(1 &lt;&lt; 63))
-CsrWrite(csr_name="mcounteren", set_mask=0x2)
-CsrWrite(csr_name="hcounteren", set_mask=0x2)
-CsrWrite(csr_name="henvcfg", set_mask=(1 &lt;&lt; 63))
-Comment(comment="VS-interrupts from VS/VU/HU serviced in HS: hie[*]=1, hideleg=0, sstatus.sie=X")
-DelegateInterrupt(causes=(), handler_mode=ExceptionHandlerMode.VS)
-ConfigureInterruptMode(mode=InterruptMode.DIRECT, handler_mode=ExceptionHandlerMode.HS)
-CsrWrite(csr_name="hie", set_mask=VS_MASK | SGEIP)
-EnableInterrupts(causes=(SSI, STI, SEI, VSEI), handler_mode=ExceptionHandlerMode.HS, global_enable=False)
-AssertInterrupt(cause=VSEI, code=[TriggerInterrupt(cause=VSEI)], expected_handler_mode=ExceptionHandlerMode.HS)
-AssertInterrupt(cause=VSSI, code=[TriggerInterrupt(cause=VSSI)], expected_handler_mode=ExceptionHandlerMode.HS)
-AssertInterrupt(cause=VSTI, code=[TriggerInterrupt(cause=VSTI)], expected_handler_mode=ExceptionHandlerMode.HS)
-AssertInterrupt(cause=SGEI, code=[TriggerInterrupt(cause=SGEI)], expected_handler_mode=ExceptionHandlerMode.HS)
-ClearInterrupt(cause=VSEI)
-ClearInterrupt(cause=VSSI)
-ClearInterrupt(cause=VSTI)
-ClearInterrupt(cause=SGEI)
-DisableInterrupts(causes=(SSI, STI, SEI), handler_mode=ExceptionHandlerMode.HS)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="272" customHeight="1" s="5">
+      <c r="E8" s="27" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" s="5" ht="272" customHeight="true">
       <c r="A9" s="23" t="inlineStr">
         <is>
           <t>SID_HINTR_007</t>
@@ -1517,7 +1536,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="288" customHeight="1" s="5">
+    <row r="10" s="5" ht="288" customHeight="true">
       <c r="A10" s="31" t="inlineStr">
         <is>
           <t>SID_HINTR_008</t>
@@ -1565,7 +1584,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="256" customHeight="1" s="5">
+    <row r="11" s="5" ht="256" customHeight="true">
       <c r="A11" s="31" t="inlineStr">
         <is>
           <t>SID_HINTR_009</t>
@@ -1617,7 +1636,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="304" customHeight="1" s="5">
+    <row r="12" s="5" ht="304" customHeight="true">
       <c r="A12" s="31" t="inlineStr">
         <is>
           <t>SID_HINTR_010</t>
@@ -1665,7 +1684,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="304" customHeight="1" s="5">
+    <row r="13" s="5" ht="304" customHeight="true">
       <c r="A13" s="31" t="inlineStr">
         <is>
           <t>SID_HINTR_011</t>
@@ -1714,7 +1733,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="225" customHeight="1" s="5">
+    <row r="14" s="5" ht="225" customHeight="true">
       <c r="A14" s="31" t="inlineStr">
         <is>
           <t>SID_HINTR_012</t>
@@ -1761,7 +1780,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="320" customHeight="1" s="5">
+    <row r="15" s="5" ht="320" customHeight="true">
       <c r="A15" s="31" t="inlineStr">
         <is>
           <t>SID_HINTR_013</t>
@@ -1804,7 +1823,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="304" customHeight="1" s="5">
+    <row r="16" s="5" ht="304" customHeight="true">
       <c r="A16" s="39" t="inlineStr">
         <is>
           <t>SID_HINTR_014</t>
@@ -1854,7 +1873,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="288" customHeight="1" s="5">
+    <row r="17" s="5" ht="288" customHeight="true">
       <c r="A17" s="39" t="inlineStr">
         <is>
           <t>SID_HINTR_017</t>
@@ -1899,7 +1918,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="144" customHeight="1" s="5">
+    <row r="18" s="5" ht="144" customHeight="true">
       <c r="A18" s="31" t="inlineStr">
         <is>
           <t>SID_HINTR_018</t>
@@ -1934,7 +1953,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="208" customHeight="1" s="5">
+    <row r="19" s="5" ht="208" customHeight="true">
       <c r="A19" s="43" t="inlineStr">
         <is>
           <t>SID_HINTR_022</t>
@@ -1971,7 +1990,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="380" customHeight="1" s="5">
+    <row r="20" s="5" ht="380" customHeight="true">
       <c r="A20" s="43" t="inlineStr">
         <is>
           <t>SID_HINTR_023</t>
@@ -2019,7 +2038,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="288" customHeight="1" s="5">
+    <row r="21" s="5" ht="288" customHeight="true">
       <c r="A21" s="43" t="inlineStr">
         <is>
           <t>SID_HINTR_024</t>
@@ -2060,15 +2079,87 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="2" t="n"/>
-      <c r="E22" s="6" t="n"/>
-    </row>
-    <row r="23">
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="2" t="n"/>
-      <c r="E23" s="6" t="n"/>
+    <row r="22" s="5" ht="150" customHeight="true">
+      <c r="A22" s="53" t="inlineStr">
+        <is>
+          <t>SID_HINTR_025</t>
+        </is>
+      </c>
+      <c r="B22" s="44" t="inlineStr">
+        <is>
+          <t>9.  Accessibility and writability of CSRs</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="inlineStr">
+        <is>
+          <t>The vstimecmp CSR is a 64-bit register and has 64-bit precision on all RV32 and RV64 systems (norm:vstimecmp_sz)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>1. Privilege mode = M-mode, so vstimecmp is accessed under its own name (a VS-mode access would go through stimecmp)
+2. Sstc enabled via menvcfg.STCE and henvcfg.STCE
+3. vstimecmp value = pick_all { 0x0123456789ABCDEF, 0xFEDCBA9876543210, 0xFFFFFFFFFFFFFFFF } - upper and lower 32-bit halves differ in every value and none is a sign-extended 32-bit immediate, so a narrow or sign-extending comparator cannot read back clean
+4. Every value is far beyond any time the test can reach, so per norm:hip_vstip_op no VS timer interrupt fires mid-scenario
+5. HS stimecmp is read either side of the sequence and must not move - the comparators are independent registers</t>
+        </is>
+      </c>
+      <c r="E22" s="54" t="inlineStr">
+        <is>
+          <t>CsrWrite(csr_name="menvcfg", set_mask=1&lt;&lt;63)   # STCE
+CsrWrite(csr_name="henvcfg", set_mask=1&lt;&lt;63)
+st_before = CsrDirectAccess(op="csrrs", csr_name="stimecmp", src1=0)
+for val in (0x0123456789ABCDEF, 0xFEDCBA9876543210, 0xFFFFFFFFFFFFFFFF):
+    v = LoadImmediateStep(imm=val)
+    CsrDirectAccess(op="csrrw", csr_name="vstimecmp", src1=v, target_is_x0=True)
+    rb = CsrDirectAccess(op="csrrs", csr_name="vstimecmp", src1=0)
+    AssertEqual(src1=rb, src2=v)
+st_after = CsrDirectAccess(op="csrrs", csr_name="stimecmp", src1=0)
+AssertEqual(src1=st_after, src2=st_before)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" s="5" ht="180" customHeight="true">
+      <c r="A23" s="53" t="inlineStr">
+        <is>
+          <t>SID_HINTR_026</t>
+        </is>
+      </c>
+      <c r="B23" s="44" t="inlineStr">
+        <is>
+          <t>9.  Accessibility and writability of CSRs</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="inlineStr">
+        <is>
+          <t>In RV32 only, accesses to the vstimecmp CSR access the low 32 bits while accesses to the vstimecmph CSR access the high 32 bits of vstimecmp (norm:vstimecmp_acc). On RV64 vstimecmph does not exist, so accessing it raises an illegal instruction exception.</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>1. Privilege mode = M-mode
+2. Sstc enabled via menvcfg.STCE and henvcfg.STCE
+3. Access = pick_all { csrrs vstimecmph, csrrw vstimecmph }
+4. Expected: ILLEGAL_INSTRUCTION on both, because on RV64 vstimecmp is a single 64-bit CSR (norm:vstimecmp_sz) and has no RV32 high half
+5. Positive control: the 64-bit vstimecmp is read first and must not trap, so the exception cannot be explained away by Sstc being off or the timer CSRs being unreachable - only the RV32 high half is absent</t>
+        </is>
+      </c>
+      <c r="E23" s="54" t="inlineStr">
+        <is>
+          <t>CsrWrite(csr_name="menvcfg", set_mask=1&lt;&lt;63)   # STCE
+CsrWrite(csr_name="henvcfg", set_mask=1&lt;&lt;63)
+# positive control: the 64-bit vstimecmp is reachable
+CsrDirectAccess(op="csrrs", csr_name="vstimecmp", src1=0)
+# the RV32 high half does not exist on RV64
+AssertException(cause=ILLEGAL_INSTRUCTION, code=[
+    CsrDirectAccess(op="csrrs", csr_name="vstimecmph", src1=0, target_is_x0=True)
+])
+zero = LoadImmediateStep(imm=0)
+AssertException(cause=ILLEGAL_INSTRUCTION, code=[
+    CsrDirectAccess(op="csrrw", csr_name="vstimecmph", src1=zero)
+])</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="C24" s="6" t="n"/>
@@ -2087,6 +2178,6 @@
     <mergeCell ref="G1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup horizontalDpi="0" orientation="portrait" verticalDpi="0"/>
 </worksheet>
 </file>